--- a/assets/templates/cnss_leave.xlsx
+++ b/assets/templates/cnss_leave.xlsx
@@ -18,26 +18,26 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="13"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="10"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -45,7 +45,7 @@
       <family val="2"/>
       <b val="1"/>
       <color theme="1"/>
-      <sz val="13"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -53,14 +53,14 @@
       <family val="2"/>
       <b val="1"/>
       <color theme="1"/>
-      <sz val="14"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="13"/>
+      <sz val="12"/>
       <u val="single"/>
       <scheme val="minor"/>
     </font>
@@ -70,6 +70,21 @@
       <b val="1"/>
       <color theme="1"/>
       <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -225,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -367,6 +382,96 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -728,1193 +833,1193 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="51" t="inlineStr">
         <is>
           <t>الصندوق الوطني</t>
         </is>
       </c>
-      <c r="B1" s="10" t="n"/>
-      <c r="C1" s="10" t="n"/>
-      <c r="D1" s="10" t="n"/>
-      <c r="E1" s="10" t="n"/>
-      <c r="F1" s="10" t="n"/>
-      <c r="G1" s="10" t="n"/>
-      <c r="H1" s="10" t="n"/>
-      <c r="I1" s="10" t="n"/>
-      <c r="J1" s="10" t="n"/>
-      <c r="K1" s="10" t="n"/>
-      <c r="L1" s="10" t="n"/>
-      <c r="M1" s="10" t="n"/>
-      <c r="N1" s="10" t="n"/>
-      <c r="O1" s="10" t="n"/>
-      <c r="P1" s="10" t="n"/>
-      <c r="Q1" s="10" t="n"/>
-      <c r="R1" s="9" t="n"/>
-      <c r="S1" s="7" t="n"/>
-      <c r="T1" s="7" t="n"/>
-      <c r="U1" s="7" t="n"/>
-      <c r="V1" s="7" t="n"/>
-      <c r="W1" s="7" t="n"/>
+      <c r="B1" s="52" t="n"/>
+      <c r="C1" s="52" t="n"/>
+      <c r="D1" s="52" t="n"/>
+      <c r="E1" s="52" t="n"/>
+      <c r="F1" s="52" t="n"/>
+      <c r="G1" s="52" t="n"/>
+      <c r="H1" s="52" t="n"/>
+      <c r="I1" s="52" t="n"/>
+      <c r="J1" s="52" t="n"/>
+      <c r="K1" s="52" t="n"/>
+      <c r="L1" s="52" t="n"/>
+      <c r="M1" s="52" t="n"/>
+      <c r="N1" s="52" t="n"/>
+      <c r="O1" s="52" t="n"/>
+      <c r="P1" s="52" t="n"/>
+      <c r="Q1" s="52" t="n"/>
+      <c r="R1" s="53" t="n"/>
+      <c r="S1" s="54" t="n"/>
+      <c r="T1" s="54" t="n"/>
+      <c r="U1" s="54" t="n"/>
+      <c r="V1" s="54" t="n"/>
+      <c r="W1" s="54" t="n"/>
     </row>
     <row r="2" ht="20.1" customHeight="1">
-      <c r="A2" s="35" t="inlineStr">
+      <c r="A2" s="55" t="inlineStr">
         <is>
           <t>للضمان الاجتماعي</t>
         </is>
       </c>
-      <c r="B2" s="34" t="n"/>
-      <c r="C2" s="7" t="n"/>
-      <c r="D2" s="7" t="n"/>
-      <c r="F2" s="7" t="n"/>
-      <c r="G2" s="7" t="n"/>
-      <c r="H2" s="7" t="n"/>
-      <c r="I2" s="7" t="n"/>
-      <c r="J2" s="7" t="n"/>
-      <c r="K2" s="7" t="n"/>
-      <c r="L2" s="7" t="n"/>
-      <c r="M2" s="7" t="n"/>
-      <c r="N2" s="7" t="n"/>
-      <c r="O2" s="7" t="n"/>
-      <c r="P2" s="7" t="n"/>
-      <c r="Q2" s="7" t="n"/>
-      <c r="R2" s="6" t="n"/>
-      <c r="S2" s="7" t="n"/>
-      <c r="T2" s="7" t="n"/>
-      <c r="U2" s="7" t="n"/>
-      <c r="V2" s="7" t="n"/>
-      <c r="W2" s="7" t="n"/>
+      <c r="B2" s="56" t="n"/>
+      <c r="C2" s="54" t="n"/>
+      <c r="D2" s="54" t="n"/>
+      <c r="F2" s="54" t="n"/>
+      <c r="G2" s="54" t="n"/>
+      <c r="H2" s="54" t="n"/>
+      <c r="I2" s="54" t="n"/>
+      <c r="J2" s="54" t="n"/>
+      <c r="K2" s="54" t="n"/>
+      <c r="L2" s="54" t="n"/>
+      <c r="M2" s="54" t="n"/>
+      <c r="N2" s="54" t="n"/>
+      <c r="O2" s="54" t="n"/>
+      <c r="P2" s="54" t="n"/>
+      <c r="Q2" s="54" t="n"/>
+      <c r="R2" s="57" t="n"/>
+      <c r="S2" s="54" t="n"/>
+      <c r="T2" s="54" t="n"/>
+      <c r="U2" s="54" t="n"/>
+      <c r="V2" s="54" t="n"/>
+      <c r="W2" s="54" t="n"/>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="48" t="inlineStr">
+      <c r="A3" s="58" t="inlineStr">
         <is>
           <t>اعــــــــــــــــــــــلام</t>
         </is>
       </c>
-      <c r="R3" s="49" t="n"/>
-      <c r="S3" s="7" t="n"/>
-      <c r="T3" s="7" t="n"/>
-      <c r="U3" s="7" t="n"/>
-      <c r="V3" s="7" t="n"/>
-      <c r="W3" s="7" t="n"/>
+      <c r="R3" s="59" t="n"/>
+      <c r="S3" s="54" t="n"/>
+      <c r="T3" s="54" t="n"/>
+      <c r="U3" s="54" t="n"/>
+      <c r="V3" s="54" t="n"/>
+      <c r="W3" s="54" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="58" t="inlineStr">
         <is>
           <t>عن ترك أجير عمله في المؤسسة (1)</t>
         </is>
       </c>
-      <c r="R4" s="49" t="n"/>
-      <c r="S4" s="7" t="n"/>
-      <c r="T4" s="7" t="n"/>
-      <c r="U4" s="7" t="n"/>
-      <c r="V4" s="7" t="n"/>
-      <c r="W4" s="7" t="n"/>
+      <c r="R4" s="59" t="n"/>
+      <c r="S4" s="54" t="n"/>
+      <c r="T4" s="54" t="n"/>
+      <c r="U4" s="54" t="n"/>
+      <c r="V4" s="54" t="n"/>
+      <c r="W4" s="54" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="7" t="n"/>
-      <c r="K5" s="7" t="n"/>
-      <c r="L5" s="7" t="n"/>
-      <c r="M5" s="7" t="n"/>
-      <c r="N5" s="7" t="n"/>
-      <c r="O5" s="7" t="n"/>
-      <c r="P5" s="7" t="n"/>
-      <c r="Q5" s="7" t="n"/>
-      <c r="R5" s="6" t="n"/>
-      <c r="S5" s="7" t="n"/>
-      <c r="T5" s="7" t="n"/>
-      <c r="U5" s="7" t="n"/>
-      <c r="V5" s="7" t="n"/>
-      <c r="W5" s="7" t="n"/>
+      <c r="A5" s="60" t="n"/>
+      <c r="B5" s="54" t="n"/>
+      <c r="C5" s="54" t="n"/>
+      <c r="D5" s="54" t="n"/>
+      <c r="E5" s="54" t="n"/>
+      <c r="F5" s="54" t="n"/>
+      <c r="G5" s="54" t="n"/>
+      <c r="H5" s="54" t="n"/>
+      <c r="I5" s="54" t="n"/>
+      <c r="J5" s="54" t="n"/>
+      <c r="K5" s="54" t="n"/>
+      <c r="L5" s="54" t="n"/>
+      <c r="M5" s="54" t="n"/>
+      <c r="N5" s="54" t="n"/>
+      <c r="O5" s="54" t="n"/>
+      <c r="P5" s="54" t="n"/>
+      <c r="Q5" s="54" t="n"/>
+      <c r="R5" s="57" t="n"/>
+      <c r="S5" s="54" t="n"/>
+      <c r="T5" s="54" t="n"/>
+      <c r="U5" s="54" t="n"/>
+      <c r="V5" s="54" t="n"/>
+      <c r="W5" s="54" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n"/>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="7" t="n"/>
-      <c r="L6" s="7" t="n"/>
-      <c r="M6" s="7" t="n"/>
-      <c r="N6" s="7" t="n"/>
-      <c r="O6" s="7" t="n"/>
-      <c r="P6" s="7" t="n"/>
-      <c r="Q6" s="7" t="n"/>
-      <c r="R6" s="6" t="n"/>
-      <c r="S6" s="7" t="n"/>
-      <c r="T6" s="7" t="n"/>
-      <c r="U6" s="7" t="n"/>
-      <c r="V6" s="7" t="n"/>
-      <c r="W6" s="7" t="n"/>
+      <c r="A6" s="60" t="n"/>
+      <c r="B6" s="54" t="n"/>
+      <c r="C6" s="54" t="n"/>
+      <c r="D6" s="54" t="n"/>
+      <c r="E6" s="54" t="n"/>
+      <c r="F6" s="54" t="n"/>
+      <c r="G6" s="54" t="n"/>
+      <c r="H6" s="54" t="n"/>
+      <c r="I6" s="54" t="n"/>
+      <c r="J6" s="54" t="n"/>
+      <c r="K6" s="54" t="n"/>
+      <c r="L6" s="54" t="n"/>
+      <c r="M6" s="54" t="n"/>
+      <c r="N6" s="54" t="n"/>
+      <c r="O6" s="54" t="n"/>
+      <c r="P6" s="54" t="n"/>
+      <c r="Q6" s="54" t="n"/>
+      <c r="R6" s="57" t="n"/>
+      <c r="S6" s="54" t="n"/>
+      <c r="T6" s="54" t="n"/>
+      <c r="U6" s="54" t="n"/>
+      <c r="V6" s="54" t="n"/>
+      <c r="W6" s="54" t="n"/>
     </row>
     <row r="7" ht="22.05" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr">
         <is>
           <t>ان صاحب العمل الموقع ادناه،</t>
         </is>
       </c>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="7" t="n"/>
-      <c r="K7" s="7" t="n"/>
-      <c r="L7" s="7" t="n"/>
-      <c r="M7" s="7" t="n"/>
-      <c r="N7" s="7" t="n"/>
-      <c r="O7" s="7" t="n"/>
-      <c r="P7" s="7" t="n"/>
-      <c r="Q7" s="7" t="n"/>
-      <c r="R7" s="6" t="n"/>
-      <c r="S7" s="7" t="n"/>
-      <c r="T7" s="47" t="n"/>
-      <c r="U7" s="7" t="n"/>
-      <c r="V7" s="7" t="n"/>
-      <c r="W7" s="7" t="n"/>
+      <c r="B7" s="54" t="n"/>
+      <c r="C7" s="54" t="n"/>
+      <c r="D7" s="54" t="n"/>
+      <c r="E7" s="54" t="n"/>
+      <c r="F7" s="54" t="n"/>
+      <c r="G7" s="54" t="n"/>
+      <c r="H7" s="54" t="n"/>
+      <c r="I7" s="54" t="n"/>
+      <c r="J7" s="54" t="n"/>
+      <c r="K7" s="54" t="n"/>
+      <c r="L7" s="54" t="n"/>
+      <c r="M7" s="54" t="n"/>
+      <c r="N7" s="54" t="n"/>
+      <c r="O7" s="54" t="n"/>
+      <c r="P7" s="54" t="n"/>
+      <c r="Q7" s="54" t="n"/>
+      <c r="R7" s="57" t="n"/>
+      <c r="S7" s="54" t="n"/>
+      <c r="T7" s="61" t="n"/>
+      <c r="U7" s="54" t="n"/>
+      <c r="V7" s="54" t="n"/>
+      <c r="W7" s="54" t="n"/>
     </row>
     <row r="8" ht="22.05" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>المسؤول عن مؤسسة :</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="21" t="n"/>
-      <c r="F8" s="7" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
-      <c r="I8" s="7" t="n"/>
-      <c r="J8" s="7" t="n"/>
-      <c r="K8" s="7" t="n"/>
-      <c r="L8" s="7" t="n"/>
-      <c r="M8" s="7" t="n"/>
-      <c r="N8" s="7" t="n"/>
-      <c r="O8" s="7" t="n"/>
-      <c r="P8" s="7" t="n"/>
-      <c r="Q8" s="7" t="n"/>
-      <c r="R8" s="6" t="n"/>
-      <c r="S8" s="7" t="n"/>
-      <c r="T8" s="7" t="n"/>
-      <c r="U8" s="7" t="n"/>
-      <c r="V8" s="7" t="n"/>
-      <c r="W8" s="7" t="n"/>
+      <c r="B8" s="54" t="n"/>
+      <c r="C8" s="54" t="n"/>
+      <c r="D8" s="54" t="n"/>
+      <c r="E8" s="61" t="n"/>
+      <c r="F8" s="54" t="n"/>
+      <c r="G8" s="54" t="n"/>
+      <c r="H8" s="54" t="n"/>
+      <c r="I8" s="54" t="n"/>
+      <c r="J8" s="54" t="n"/>
+      <c r="K8" s="54" t="n"/>
+      <c r="L8" s="54" t="n"/>
+      <c r="M8" s="54" t="n"/>
+      <c r="N8" s="54" t="n"/>
+      <c r="O8" s="54" t="n"/>
+      <c r="P8" s="54" t="n"/>
+      <c r="Q8" s="54" t="n"/>
+      <c r="R8" s="57" t="n"/>
+      <c r="S8" s="54" t="n"/>
+      <c r="T8" s="54" t="n"/>
+      <c r="U8" s="54" t="n"/>
+      <c r="V8" s="54" t="n"/>
+      <c r="W8" s="54" t="n"/>
     </row>
     <row r="9" ht="22.05" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr">
         <is>
           <t>المسجلة في الصندوق الوطني للضمان الاجتماعي تحت رقم:</t>
         </is>
       </c>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
-      <c r="I9" s="7" t="n"/>
-      <c r="J9" s="7" t="n"/>
-      <c r="K9" s="7" t="n"/>
-      <c r="L9" s="7" t="n"/>
-      <c r="M9" s="7" t="n"/>
-      <c r="N9" s="32" t="n"/>
-      <c r="O9" s="29" t="n"/>
-      <c r="P9" s="29" t="n"/>
-      <c r="Q9" s="7" t="n"/>
-      <c r="R9" s="6" t="n"/>
-      <c r="S9" s="7" t="n"/>
-      <c r="T9" s="7" t="n"/>
-      <c r="U9" s="7" t="n"/>
-      <c r="V9" s="7" t="n"/>
-      <c r="W9" s="7" t="n"/>
+      <c r="B9" s="54" t="n"/>
+      <c r="C9" s="54" t="n"/>
+      <c r="D9" s="54" t="n"/>
+      <c r="E9" s="54" t="n"/>
+      <c r="F9" s="54" t="n"/>
+      <c r="G9" s="54" t="n"/>
+      <c r="H9" s="54" t="n"/>
+      <c r="I9" s="54" t="n"/>
+      <c r="J9" s="54" t="n"/>
+      <c r="K9" s="54" t="n"/>
+      <c r="L9" s="54" t="n"/>
+      <c r="M9" s="54" t="n"/>
+      <c r="N9" s="62" t="n"/>
+      <c r="O9" s="63" t="n"/>
+      <c r="P9" s="63" t="n"/>
+      <c r="Q9" s="54" t="n"/>
+      <c r="R9" s="57" t="n"/>
+      <c r="S9" s="54" t="n"/>
+      <c r="T9" s="54" t="n"/>
+      <c r="U9" s="54" t="n"/>
+      <c r="V9" s="54" t="n"/>
+      <c r="W9" s="54" t="n"/>
     </row>
     <row r="10" ht="22.05" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="60" t="inlineStr">
         <is>
           <t>سجل تجاري: مكان................................... رقم.............................. هاتف</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
-      <c r="F10" s="7" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="7" t="n"/>
-      <c r="K10" s="7" t="n"/>
-      <c r="L10" s="41" t="n"/>
-      <c r="N10" s="31" t="n"/>
-      <c r="O10" s="7" t="n"/>
-      <c r="P10" s="7" t="n"/>
-      <c r="Q10" s="7" t="n"/>
-      <c r="R10" s="6" t="n"/>
-      <c r="S10" s="7" t="n"/>
-      <c r="T10" s="7" t="n"/>
-      <c r="U10" s="7" t="n"/>
-      <c r="V10" s="7" t="n"/>
-      <c r="W10" s="7" t="n"/>
+      <c r="B10" s="54" t="n"/>
+      <c r="C10" s="54" t="n"/>
+      <c r="D10" s="54" t="n"/>
+      <c r="E10" s="54" t="n"/>
+      <c r="F10" s="54" t="n"/>
+      <c r="G10" s="54" t="n"/>
+      <c r="H10" s="54" t="n"/>
+      <c r="I10" s="54" t="n"/>
+      <c r="J10" s="54" t="n"/>
+      <c r="K10" s="54" t="n"/>
+      <c r="L10" s="46" t="n"/>
+      <c r="N10" s="64" t="n"/>
+      <c r="O10" s="54" t="n"/>
+      <c r="P10" s="54" t="n"/>
+      <c r="Q10" s="54" t="n"/>
+      <c r="R10" s="57" t="n"/>
+      <c r="S10" s="54" t="n"/>
+      <c r="T10" s="54" t="n"/>
+      <c r="U10" s="54" t="n"/>
+      <c r="V10" s="54" t="n"/>
+      <c r="W10" s="54" t="n"/>
     </row>
     <row r="11" ht="22.05" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="60" t="inlineStr">
         <is>
           <t>وعنوانها الكامل:</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="7" t="n"/>
-      <c r="K11" s="7" t="n"/>
-      <c r="L11" s="7" t="n"/>
-      <c r="M11" s="7" t="n"/>
-      <c r="N11" s="7" t="n"/>
-      <c r="O11" s="7" t="n"/>
-      <c r="P11" s="7" t="n"/>
-      <c r="Q11" s="7" t="n"/>
-      <c r="R11" s="6" t="n"/>
-      <c r="S11" s="7" t="n"/>
-      <c r="T11" s="7" t="n"/>
-      <c r="U11" s="7" t="n"/>
-      <c r="V11" s="7" t="n"/>
-      <c r="W11" s="7" t="n"/>
+      <c r="B11" s="54" t="n"/>
+      <c r="C11" s="61" t="n"/>
+      <c r="D11" s="54" t="n"/>
+      <c r="E11" s="54" t="n"/>
+      <c r="F11" s="54" t="n"/>
+      <c r="G11" s="54" t="n"/>
+      <c r="H11" s="54" t="n"/>
+      <c r="I11" s="54" t="n"/>
+      <c r="J11" s="54" t="n"/>
+      <c r="K11" s="54" t="n"/>
+      <c r="L11" s="54" t="n"/>
+      <c r="M11" s="54" t="n"/>
+      <c r="N11" s="54" t="n"/>
+      <c r="O11" s="54" t="n"/>
+      <c r="P11" s="54" t="n"/>
+      <c r="Q11" s="54" t="n"/>
+      <c r="R11" s="57" t="n"/>
+      <c r="S11" s="54" t="n"/>
+      <c r="T11" s="54" t="n"/>
+      <c r="U11" s="54" t="n"/>
+      <c r="V11" s="54" t="n"/>
+      <c r="W11" s="54" t="n"/>
     </row>
     <row r="12" ht="22.05" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="60" t="inlineStr">
         <is>
           <t>...............................................................................................................................</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
-      <c r="F12" s="7" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="7" t="n"/>
-      <c r="K12" s="7" t="n"/>
-      <c r="L12" s="7" t="n"/>
-      <c r="M12" s="7" t="n"/>
-      <c r="N12" s="7" t="n"/>
-      <c r="O12" s="7" t="n"/>
-      <c r="P12" s="7" t="n"/>
-      <c r="Q12" s="7" t="n"/>
-      <c r="R12" s="6" t="n"/>
-      <c r="S12" s="7" t="n"/>
-      <c r="T12" s="7" t="n"/>
-      <c r="U12" s="7" t="n"/>
-      <c r="V12" s="7" t="n"/>
-      <c r="W12" s="7" t="n"/>
+      <c r="B12" s="54" t="n"/>
+      <c r="C12" s="54" t="n"/>
+      <c r="D12" s="54" t="n"/>
+      <c r="E12" s="54" t="n"/>
+      <c r="F12" s="54" t="n"/>
+      <c r="G12" s="54" t="n"/>
+      <c r="H12" s="54" t="n"/>
+      <c r="I12" s="54" t="n"/>
+      <c r="J12" s="54" t="n"/>
+      <c r="K12" s="54" t="n"/>
+      <c r="L12" s="54" t="n"/>
+      <c r="M12" s="54" t="n"/>
+      <c r="N12" s="54" t="n"/>
+      <c r="O12" s="54" t="n"/>
+      <c r="P12" s="54" t="n"/>
+      <c r="Q12" s="54" t="n"/>
+      <c r="R12" s="57" t="n"/>
+      <c r="S12" s="54" t="n"/>
+      <c r="T12" s="54" t="n"/>
+      <c r="U12" s="54" t="n"/>
+      <c r="V12" s="54" t="n"/>
+      <c r="W12" s="54" t="n"/>
     </row>
     <row r="13" ht="22.05" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="60" t="inlineStr">
         <is>
           <t>يصرح بأن الأجير المبينة هويته فيما يلي والمسجل في الصندوق تحت الرقم</t>
         </is>
       </c>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="n"/>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
-      <c r="I13" s="7" t="n"/>
-      <c r="J13" s="7" t="n"/>
-      <c r="K13" s="7" t="n"/>
-      <c r="L13" s="7" t="n"/>
-      <c r="M13" s="7" t="n"/>
-      <c r="N13" s="29" t="n"/>
-      <c r="O13" s="50" t="n"/>
-      <c r="P13" s="30" t="n"/>
-      <c r="Q13" s="7" t="n"/>
-      <c r="R13" s="6" t="n"/>
-      <c r="S13" s="7" t="n"/>
-      <c r="T13" s="7" t="n"/>
-      <c r="U13" s="7" t="n"/>
-      <c r="V13" s="7" t="n"/>
-      <c r="W13" s="7" t="n"/>
+      <c r="B13" s="54" t="n"/>
+      <c r="C13" s="54" t="n"/>
+      <c r="D13" s="54" t="n"/>
+      <c r="E13" s="54" t="n"/>
+      <c r="F13" s="54" t="n"/>
+      <c r="G13" s="54" t="n"/>
+      <c r="H13" s="54" t="n"/>
+      <c r="I13" s="54" t="n"/>
+      <c r="J13" s="54" t="n"/>
+      <c r="K13" s="54" t="n"/>
+      <c r="L13" s="54" t="n"/>
+      <c r="M13" s="54" t="n"/>
+      <c r="N13" s="63" t="n"/>
+      <c r="O13" s="65" t="n"/>
+      <c r="P13" s="66" t="n"/>
+      <c r="Q13" s="54" t="n"/>
+      <c r="R13" s="57" t="n"/>
+      <c r="S13" s="54" t="n"/>
+      <c r="T13" s="54" t="n"/>
+      <c r="U13" s="54" t="n"/>
+      <c r="V13" s="54" t="n"/>
+      <c r="W13" s="54" t="n"/>
     </row>
     <row r="14" ht="22.05" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="60" t="inlineStr">
         <is>
           <t>الجنس:</t>
         </is>
       </c>
-      <c r="B14" s="39" t="inlineStr">
+      <c r="B14" s="67" t="inlineStr">
         <is>
           <t>ذكر</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="68" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D14" s="39" t="n"/>
-      <c r="E14" s="39" t="inlineStr">
+      <c r="D14" s="67" t="n"/>
+      <c r="E14" s="67" t="inlineStr">
         <is>
           <t>انثى</t>
         </is>
       </c>
-      <c r="F14" s="29" t="inlineStr">
+      <c r="F14" s="63" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
-      <c r="I14" s="7" t="n"/>
-      <c r="J14" s="7" t="n"/>
-      <c r="K14" s="7" t="n"/>
-      <c r="L14" s="7" t="n"/>
-      <c r="M14" s="7" t="n"/>
-      <c r="N14" s="7" t="n"/>
-      <c r="O14" s="7" t="n"/>
-      <c r="P14" s="7" t="n"/>
-      <c r="Q14" s="7" t="n"/>
-      <c r="R14" s="6" t="n"/>
-      <c r="S14" s="7" t="n"/>
-      <c r="T14" s="7" t="n"/>
-      <c r="U14" s="7" t="n"/>
-      <c r="V14" s="7" t="n"/>
-      <c r="W14" s="7" t="n"/>
+      <c r="G14" s="54" t="n"/>
+      <c r="H14" s="54" t="n"/>
+      <c r="I14" s="54" t="n"/>
+      <c r="J14" s="54" t="n"/>
+      <c r="K14" s="54" t="n"/>
+      <c r="L14" s="54" t="n"/>
+      <c r="M14" s="54" t="n"/>
+      <c r="N14" s="54" t="n"/>
+      <c r="O14" s="54" t="n"/>
+      <c r="P14" s="54" t="n"/>
+      <c r="Q14" s="54" t="n"/>
+      <c r="R14" s="57" t="n"/>
+      <c r="S14" s="54" t="n"/>
+      <c r="T14" s="54" t="n"/>
+      <c r="U14" s="54" t="n"/>
+      <c r="V14" s="54" t="n"/>
+      <c r="W14" s="54" t="n"/>
     </row>
     <row r="15" ht="22.05" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="60" t="inlineStr">
         <is>
           <t>اسم الأجير:</t>
         </is>
       </c>
-      <c r="B15" s="21" t="n"/>
-      <c r="C15" s="21" t="n"/>
-      <c r="D15" s="21" t="n"/>
-      <c r="E15" s="21" t="n"/>
-      <c r="F15" s="21" t="n"/>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="B15" s="61" t="n"/>
+      <c r="C15" s="61" t="n"/>
+      <c r="D15" s="61" t="n"/>
+      <c r="E15" s="61" t="n"/>
+      <c r="F15" s="61" t="n"/>
+      <c r="G15" s="54" t="inlineStr">
         <is>
           <t>الشهرة</t>
         </is>
       </c>
-      <c r="H15" s="7" t="n"/>
-      <c r="I15" s="21" t="n"/>
-      <c r="J15" s="7" t="n"/>
-      <c r="K15" s="7" t="n"/>
-      <c r="L15" s="7" t="n"/>
-      <c r="M15" s="7" t="n"/>
-      <c r="N15" s="7" t="n"/>
-      <c r="O15" s="7" t="n"/>
-      <c r="P15" s="7" t="n"/>
-      <c r="Q15" s="7" t="n"/>
-      <c r="R15" s="6" t="n"/>
-      <c r="S15" s="7" t="n"/>
-      <c r="T15" s="7" t="n"/>
-      <c r="U15" s="7" t="n"/>
-      <c r="V15" s="7" t="n"/>
-      <c r="W15" s="7" t="n"/>
+      <c r="H15" s="54" t="n"/>
+      <c r="I15" s="61" t="n"/>
+      <c r="J15" s="54" t="n"/>
+      <c r="K15" s="54" t="n"/>
+      <c r="L15" s="54" t="n"/>
+      <c r="M15" s="54" t="n"/>
+      <c r="N15" s="54" t="n"/>
+      <c r="O15" s="54" t="n"/>
+      <c r="P15" s="54" t="n"/>
+      <c r="Q15" s="54" t="n"/>
+      <c r="R15" s="57" t="n"/>
+      <c r="S15" s="54" t="n"/>
+      <c r="T15" s="54" t="n"/>
+      <c r="U15" s="54" t="n"/>
+      <c r="V15" s="54" t="n"/>
+      <c r="W15" s="54" t="n"/>
     </row>
     <row r="16" ht="22.05" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="60" t="inlineStr">
         <is>
           <t>اسم الاب:</t>
         </is>
       </c>
-      <c r="B16" s="21" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="47" t="n"/>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="B16" s="61" t="n"/>
+      <c r="C16" s="54" t="n"/>
+      <c r="D16" s="54" t="n"/>
+      <c r="E16" s="54" t="n"/>
+      <c r="F16" s="61" t="n"/>
+      <c r="G16" s="54" t="inlineStr">
         <is>
           <t>اسم الأم وشهرتها:</t>
         </is>
       </c>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n"/>
-      <c r="J16" s="7" t="n"/>
-      <c r="K16" s="21" t="n"/>
-      <c r="L16" s="7" t="n"/>
-      <c r="M16" s="7" t="n"/>
-      <c r="N16" s="7" t="n"/>
-      <c r="O16" s="7" t="n"/>
-      <c r="P16" s="7" t="n"/>
-      <c r="Q16" s="7" t="n"/>
-      <c r="R16" s="6" t="n"/>
-      <c r="S16" s="7" t="n"/>
-      <c r="T16" s="7" t="n"/>
-      <c r="U16" s="7" t="n"/>
-      <c r="V16" s="7" t="n"/>
-      <c r="W16" s="7" t="n"/>
+      <c r="H16" s="54" t="n"/>
+      <c r="I16" s="54" t="n"/>
+      <c r="J16" s="54" t="n"/>
+      <c r="K16" s="61" t="n"/>
+      <c r="L16" s="54" t="n"/>
+      <c r="M16" s="54" t="n"/>
+      <c r="N16" s="54" t="n"/>
+      <c r="O16" s="54" t="n"/>
+      <c r="P16" s="54" t="n"/>
+      <c r="Q16" s="54" t="n"/>
+      <c r="R16" s="57" t="n"/>
+      <c r="S16" s="54" t="n"/>
+      <c r="T16" s="54" t="n"/>
+      <c r="U16" s="54" t="n"/>
+      <c r="V16" s="54" t="n"/>
+      <c r="W16" s="54" t="n"/>
     </row>
     <row r="17" ht="22.05" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="60" t="inlineStr">
         <is>
           <t>تاريخ ومحل ولادة الاجير:</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="47" t="n"/>
-      <c r="E17" s="7" t="n"/>
+      <c r="B17" s="54" t="n"/>
+      <c r="C17" s="54" t="n"/>
+      <c r="D17" s="61" t="n"/>
+      <c r="E17" s="54" t="n"/>
       <c r="F17" s="45" t="n"/>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="H17" s="54" t="inlineStr">
         <is>
           <t>رقم السجل:</t>
         </is>
       </c>
-      <c r="I17" s="7" t="n"/>
-      <c r="J17" s="7" t="n"/>
-      <c r="K17" s="28" t="n"/>
-      <c r="L17" s="7" t="n"/>
-      <c r="M17" s="7" t="inlineStr">
+      <c r="I17" s="54" t="n"/>
+      <c r="J17" s="54" t="n"/>
+      <c r="K17" s="46" t="n"/>
+      <c r="L17" s="54" t="n"/>
+      <c r="M17" s="54" t="inlineStr">
         <is>
           <t>الجنسية:</t>
         </is>
       </c>
-      <c r="N17" s="7" t="n"/>
-      <c r="O17" s="21" t="n"/>
-      <c r="P17" s="7" t="n"/>
-      <c r="Q17" s="7" t="n"/>
-      <c r="R17" s="6" t="n"/>
-      <c r="S17" s="7" t="n"/>
-      <c r="T17" s="7" t="n"/>
-      <c r="U17" s="7" t="n"/>
-      <c r="V17" s="7" t="n"/>
-      <c r="W17" s="7" t="n"/>
+      <c r="N17" s="54" t="n"/>
+      <c r="O17" s="61" t="n"/>
+      <c r="P17" s="54" t="n"/>
+      <c r="Q17" s="54" t="n"/>
+      <c r="R17" s="57" t="n"/>
+      <c r="S17" s="54" t="n"/>
+      <c r="T17" s="54" t="n"/>
+      <c r="U17" s="54" t="n"/>
+      <c r="V17" s="54" t="n"/>
+      <c r="W17" s="54" t="n"/>
     </row>
     <row r="18" ht="22.05" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">الوضع العائلي: أعزب </t>
         </is>
       </c>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="B18" s="54" t="n"/>
+      <c r="C18" s="54" t="n"/>
+      <c r="D18" s="68" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="54" t="inlineStr">
         <is>
           <t>متأهل</t>
         </is>
       </c>
-      <c r="F18" s="36" t="inlineStr">
+      <c r="F18" s="63" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G18" s="54" t="inlineStr">
         <is>
           <t>ارمل</t>
         </is>
       </c>
-      <c r="H18" s="24" t="inlineStr">
+      <c r="H18" s="68" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="54" t="inlineStr">
         <is>
           <t>مطلّق</t>
         </is>
       </c>
-      <c r="J18" s="24" t="inlineStr">
+      <c r="J18" s="68" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K18" s="7" t="inlineStr">
+      <c r="K18" s="54" t="inlineStr">
         <is>
           <t>هاجر</t>
         </is>
       </c>
-      <c r="L18" s="24" t="inlineStr">
+      <c r="L18" s="68" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="M18" s="7" t="n"/>
-      <c r="N18" s="7" t="n"/>
-      <c r="O18" s="7" t="n"/>
-      <c r="P18" s="7" t="n"/>
-      <c r="Q18" s="7" t="n"/>
-      <c r="R18" s="6" t="n"/>
-      <c r="S18" s="7" t="n"/>
-      <c r="T18" s="7" t="n"/>
-      <c r="U18" s="7" t="n"/>
-      <c r="V18" s="7" t="n"/>
-      <c r="W18" s="7" t="n"/>
+      <c r="M18" s="54" t="n"/>
+      <c r="N18" s="54" t="n"/>
+      <c r="O18" s="54" t="n"/>
+      <c r="P18" s="54" t="n"/>
+      <c r="Q18" s="54" t="n"/>
+      <c r="R18" s="57" t="n"/>
+      <c r="S18" s="54" t="n"/>
+      <c r="T18" s="54" t="n"/>
+      <c r="U18" s="54" t="n"/>
+      <c r="V18" s="54" t="n"/>
+      <c r="W18" s="54" t="n"/>
     </row>
     <row r="19" ht="22.05" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="60" t="inlineStr">
         <is>
           <t>ترك العمل بها منذ:</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="27" t="n"/>
-      <c r="D19" s="41" t="inlineStr">
+      <c r="B19" s="54" t="n"/>
+      <c r="C19" s="69" t="n"/>
+      <c r="D19" s="46" t="inlineStr">
         <is>
           <t>_</t>
         </is>
       </c>
-      <c r="E19" s="41" t="n"/>
-      <c r="F19" s="21" t="n"/>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="7" t="n"/>
-      <c r="I19" s="7" t="n"/>
-      <c r="J19" s="7" t="n"/>
-      <c r="K19" s="7" t="n"/>
-      <c r="L19" s="7" t="n"/>
-      <c r="M19" s="7" t="n"/>
-      <c r="N19" s="7" t="n"/>
-      <c r="O19" s="7" t="n"/>
-      <c r="P19" s="7" t="n"/>
-      <c r="Q19" s="7" t="n"/>
-      <c r="R19" s="6" t="n"/>
-      <c r="S19" s="7" t="n"/>
-      <c r="T19" s="7" t="n"/>
-      <c r="U19" s="7" t="n"/>
-      <c r="V19" s="7" t="n"/>
-      <c r="W19" s="7" t="n"/>
+      <c r="E19" s="46" t="n"/>
+      <c r="F19" s="61" t="n"/>
+      <c r="G19" s="54" t="n"/>
+      <c r="H19" s="54" t="n"/>
+      <c r="I19" s="54" t="n"/>
+      <c r="J19" s="54" t="n"/>
+      <c r="K19" s="54" t="n"/>
+      <c r="L19" s="54" t="n"/>
+      <c r="M19" s="54" t="n"/>
+      <c r="N19" s="54" t="n"/>
+      <c r="O19" s="54" t="n"/>
+      <c r="P19" s="54" t="n"/>
+      <c r="Q19" s="54" t="n"/>
+      <c r="R19" s="57" t="n"/>
+      <c r="S19" s="54" t="n"/>
+      <c r="T19" s="54" t="n"/>
+      <c r="U19" s="54" t="n"/>
+      <c r="V19" s="54" t="n"/>
+      <c r="W19" s="54" t="n"/>
     </row>
     <row r="20" ht="22.05" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="60" t="inlineStr">
         <is>
           <t>سبب ترك العمل:</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="36" t="inlineStr">
+      <c r="B20" s="54" t="n"/>
+      <c r="C20" s="63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="39" t="inlineStr">
+      <c r="D20" s="67" t="inlineStr">
         <is>
           <t>استقالة</t>
         </is>
       </c>
-      <c r="E20" s="24" t="inlineStr">
+      <c r="E20" s="68" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F20" s="39" t="inlineStr">
+      <c r="F20" s="67" t="inlineStr">
         <is>
           <t>بلوغ السن</t>
         </is>
       </c>
-      <c r="G20" s="24" t="inlineStr">
+      <c r="G20" s="68" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H20" s="39" t="inlineStr">
+      <c r="H20" s="67" t="inlineStr">
         <is>
           <t>عجز</t>
         </is>
       </c>
-      <c r="I20" s="24" t="inlineStr">
+      <c r="I20" s="68" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J20" s="23" t="inlineStr">
+      <c r="J20" s="70" t="inlineStr">
         <is>
           <t>زواج</t>
         </is>
       </c>
-      <c r="K20" s="24" t="inlineStr">
+      <c r="K20" s="68" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L20" s="39" t="inlineStr">
+      <c r="L20" s="67" t="inlineStr">
         <is>
           <t>وفاة</t>
         </is>
       </c>
-      <c r="M20" s="24" t="inlineStr">
+      <c r="M20" s="68" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="N20" s="39" t="inlineStr">
+      <c r="N20" s="67" t="inlineStr">
         <is>
           <t>هجرة</t>
         </is>
       </c>
-      <c r="O20" s="24" t="inlineStr">
+      <c r="O20" s="68" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P20" s="38" t="inlineStr">
+      <c r="P20" s="71" t="inlineStr">
         <is>
           <t>عمل آخر</t>
         </is>
       </c>
-      <c r="R20" s="23" t="n"/>
-      <c r="S20" s="7" t="n"/>
-      <c r="T20" s="7" t="n"/>
-      <c r="U20" s="7" t="n"/>
-      <c r="V20" s="7" t="n"/>
-      <c r="W20" s="7" t="n"/>
+      <c r="R20" s="70" t="n"/>
+      <c r="S20" s="54" t="n"/>
+      <c r="T20" s="54" t="n"/>
+      <c r="U20" s="54" t="n"/>
+      <c r="V20" s="54" t="n"/>
+      <c r="W20" s="54" t="n"/>
     </row>
     <row r="21" ht="22.05" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="60" t="inlineStr">
         <is>
           <t>عمل الاجير الحالي:</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="21" t="n"/>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="7" t="n"/>
-      <c r="I21" s="7" t="n"/>
-      <c r="J21" s="7" t="n"/>
-      <c r="K21" s="7" t="n"/>
-      <c r="L21" s="7" t="n"/>
-      <c r="M21" s="7" t="n"/>
-      <c r="N21" s="7" t="n"/>
-      <c r="O21" s="7" t="n"/>
-      <c r="P21" s="7" t="n"/>
-      <c r="Q21" s="7" t="n"/>
-      <c r="R21" s="6" t="n"/>
-      <c r="S21" s="7" t="n"/>
-      <c r="T21" s="7" t="n"/>
-      <c r="U21" s="7" t="n"/>
-      <c r="V21" s="7" t="n"/>
-      <c r="W21" s="7" t="n"/>
+      <c r="B21" s="54" t="n"/>
+      <c r="C21" s="54" t="n"/>
+      <c r="D21" s="61" t="n"/>
+      <c r="E21" s="54" t="n"/>
+      <c r="F21" s="54" t="n"/>
+      <c r="G21" s="54" t="n"/>
+      <c r="H21" s="54" t="n"/>
+      <c r="I21" s="54" t="n"/>
+      <c r="J21" s="54" t="n"/>
+      <c r="K21" s="54" t="n"/>
+      <c r="L21" s="54" t="n"/>
+      <c r="M21" s="54" t="n"/>
+      <c r="N21" s="54" t="n"/>
+      <c r="O21" s="54" t="n"/>
+      <c r="P21" s="54" t="n"/>
+      <c r="Q21" s="54" t="n"/>
+      <c r="R21" s="57" t="n"/>
+      <c r="S21" s="54" t="n"/>
+      <c r="T21" s="54" t="n"/>
+      <c r="U21" s="54" t="n"/>
+      <c r="V21" s="54" t="n"/>
+      <c r="W21" s="54" t="n"/>
     </row>
     <row r="22" ht="22.05" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">ان راتب الاجير بتاريخ ترك العمل هو: </t>
         </is>
       </c>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="37" t="n"/>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="B22" s="54" t="n"/>
+      <c r="C22" s="54" t="n"/>
+      <c r="D22" s="54" t="n"/>
+      <c r="E22" s="54" t="n"/>
+      <c r="F22" s="72" t="n"/>
+      <c r="H22" s="73" t="inlineStr">
         <is>
           <t>ل.ل</t>
         </is>
       </c>
-      <c r="I22" s="21" t="n"/>
-      <c r="J22" s="7" t="n"/>
-      <c r="K22" s="7" t="n"/>
-      <c r="L22" s="7" t="n"/>
-      <c r="M22" s="7" t="n"/>
-      <c r="N22" s="7" t="n"/>
-      <c r="O22" s="7" t="n"/>
-      <c r="P22" s="7" t="n"/>
-      <c r="Q22" s="7" t="n"/>
-      <c r="R22" s="6" t="n"/>
-      <c r="S22" s="7" t="n"/>
-      <c r="T22" s="7" t="n"/>
-      <c r="U22" s="7" t="n"/>
-      <c r="V22" s="7" t="n"/>
-      <c r="W22" s="7" t="n"/>
+      <c r="I22" s="61" t="n"/>
+      <c r="J22" s="54" t="n"/>
+      <c r="K22" s="54" t="n"/>
+      <c r="L22" s="54" t="n"/>
+      <c r="M22" s="54" t="n"/>
+      <c r="N22" s="54" t="n"/>
+      <c r="O22" s="54" t="n"/>
+      <c r="P22" s="54" t="n"/>
+      <c r="Q22" s="54" t="n"/>
+      <c r="R22" s="57" t="n"/>
+      <c r="S22" s="54" t="n"/>
+      <c r="T22" s="54" t="n"/>
+      <c r="U22" s="54" t="n"/>
+      <c r="V22" s="54" t="n"/>
+      <c r="W22" s="54" t="n"/>
     </row>
     <row r="23" ht="25.05" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="60" t="inlineStr">
         <is>
           <t>بيروت في ..........................200                       خاتم المؤسسة       اسم المسؤول عن المؤسسة وتوقيعه</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="7" t="n"/>
-      <c r="I23" s="7" t="n"/>
-      <c r="J23" s="7" t="n"/>
-      <c r="K23" s="7" t="n"/>
-      <c r="L23" s="7" t="n"/>
-      <c r="M23" s="7" t="n"/>
-      <c r="N23" s="7" t="n"/>
-      <c r="O23" s="7" t="n"/>
-      <c r="P23" s="7" t="n"/>
-      <c r="Q23" s="7" t="n"/>
-      <c r="R23" s="6" t="n"/>
-      <c r="S23" s="7" t="n"/>
-      <c r="T23" s="7" t="n"/>
-      <c r="U23" s="7" t="n"/>
-      <c r="V23" s="7" t="n"/>
-      <c r="W23" s="7" t="n"/>
+      <c r="B23" s="54" t="n"/>
+      <c r="C23" s="54" t="n"/>
+      <c r="D23" s="54" t="n"/>
+      <c r="E23" s="54" t="n"/>
+      <c r="F23" s="54" t="n"/>
+      <c r="G23" s="54" t="n"/>
+      <c r="H23" s="54" t="n"/>
+      <c r="I23" s="54" t="n"/>
+      <c r="J23" s="54" t="n"/>
+      <c r="K23" s="54" t="n"/>
+      <c r="L23" s="54" t="n"/>
+      <c r="M23" s="54" t="n"/>
+      <c r="N23" s="54" t="n"/>
+      <c r="O23" s="54" t="n"/>
+      <c r="P23" s="54" t="n"/>
+      <c r="Q23" s="54" t="n"/>
+      <c r="R23" s="57" t="n"/>
+      <c r="S23" s="54" t="n"/>
+      <c r="T23" s="54" t="n"/>
+      <c r="U23" s="54" t="n"/>
+      <c r="V23" s="54" t="n"/>
+      <c r="W23" s="54" t="n"/>
     </row>
     <row r="24" ht="67.2" customHeight="1">
-      <c r="A24" s="12" t="n"/>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="4" t="n"/>
-      <c r="K24" s="20" t="n"/>
-      <c r="L24" s="19" t="n"/>
-      <c r="M24" s="19" t="n"/>
-      <c r="N24" s="4" t="n"/>
-      <c r="O24" s="4" t="n"/>
-      <c r="P24" s="4" t="n"/>
-      <c r="Q24" s="4" t="n"/>
-      <c r="R24" s="3" t="n"/>
-      <c r="S24" s="7" t="n"/>
-      <c r="T24" s="7" t="n"/>
-      <c r="U24" s="7" t="n"/>
-      <c r="V24" s="7" t="n"/>
-      <c r="W24" s="7" t="n"/>
+      <c r="A24" s="74" t="n"/>
+      <c r="B24" s="75" t="n"/>
+      <c r="C24" s="75" t="n"/>
+      <c r="D24" s="75" t="n"/>
+      <c r="E24" s="75" t="n"/>
+      <c r="F24" s="75" t="n"/>
+      <c r="G24" s="75" t="n"/>
+      <c r="H24" s="75" t="n"/>
+      <c r="I24" s="75" t="n"/>
+      <c r="J24" s="75" t="n"/>
+      <c r="K24" s="76" t="n"/>
+      <c r="L24" s="77" t="n"/>
+      <c r="M24" s="77" t="n"/>
+      <c r="N24" s="75" t="n"/>
+      <c r="O24" s="75" t="n"/>
+      <c r="P24" s="75" t="n"/>
+      <c r="Q24" s="75" t="n"/>
+      <c r="R24" s="78" t="n"/>
+      <c r="S24" s="54" t="n"/>
+      <c r="T24" s="54" t="n"/>
+      <c r="U24" s="54" t="n"/>
+      <c r="V24" s="54" t="n"/>
+      <c r="W24" s="54" t="n"/>
     </row>
     <row r="25" ht="20.1" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="51" t="inlineStr">
         <is>
           <t xml:space="preserve">أوافق على صحة المعلومات المدرجة أعلاه:                   </t>
         </is>
       </c>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="10" t="n"/>
-      <c r="F25" s="10" t="n"/>
-      <c r="G25" s="10" t="n"/>
-      <c r="H25" s="18" t="inlineStr">
+      <c r="B25" s="52" t="n"/>
+      <c r="C25" s="52" t="n"/>
+      <c r="D25" s="52" t="n"/>
+      <c r="E25" s="52" t="n"/>
+      <c r="F25" s="52" t="n"/>
+      <c r="G25" s="52" t="n"/>
+      <c r="H25" s="79" t="inlineStr">
         <is>
           <t>اسم الاجير :</t>
         </is>
       </c>
-      <c r="I25" s="10" t="n"/>
-      <c r="J25" s="10" t="n"/>
-      <c r="K25" s="17" t="n"/>
-      <c r="L25" s="16" t="n"/>
-      <c r="M25" s="10" t="n"/>
-      <c r="N25" s="10" t="n"/>
-      <c r="O25" s="10" t="n"/>
-      <c r="P25" s="10" t="n"/>
-      <c r="Q25" s="10" t="n"/>
-      <c r="R25" s="9" t="n"/>
-      <c r="S25" s="7" t="n"/>
-      <c r="T25" s="7" t="n"/>
-      <c r="U25" s="7" t="n"/>
-      <c r="V25" s="7" t="n"/>
-      <c r="W25" s="7" t="n"/>
+      <c r="I25" s="52" t="n"/>
+      <c r="J25" s="52" t="n"/>
+      <c r="K25" s="80" t="n"/>
+      <c r="L25" s="81" t="n"/>
+      <c r="M25" s="52" t="n"/>
+      <c r="N25" s="52" t="n"/>
+      <c r="O25" s="52" t="n"/>
+      <c r="P25" s="52" t="n"/>
+      <c r="Q25" s="52" t="n"/>
+      <c r="R25" s="53" t="n"/>
+      <c r="S25" s="54" t="n"/>
+      <c r="T25" s="54" t="n"/>
+      <c r="U25" s="54" t="n"/>
+      <c r="V25" s="54" t="n"/>
+      <c r="W25" s="54" t="n"/>
     </row>
     <row r="26" ht="20.1" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="74" t="inlineStr">
         <is>
           <t>التاريخ...........................................</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="14" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="B26" s="75" t="n"/>
+      <c r="C26" s="75" t="n"/>
+      <c r="D26" s="75" t="n"/>
+      <c r="E26" s="82" t="n"/>
+      <c r="F26" s="75" t="n"/>
+      <c r="G26" s="75" t="n"/>
+      <c r="H26" s="54" t="inlineStr">
         <is>
           <t>التوقيع     :       ..............................................</t>
         </is>
       </c>
-      <c r="I26" s="7" t="n"/>
-      <c r="J26" s="7" t="n"/>
-      <c r="K26" s="7" t="inlineStr">
+      <c r="I26" s="54" t="n"/>
+      <c r="J26" s="54" t="n"/>
+      <c r="K26" s="54" t="inlineStr">
         <is>
           <t>.........................................................</t>
         </is>
       </c>
-      <c r="L26" s="7" t="n"/>
-      <c r="M26" s="7" t="n"/>
-      <c r="N26" s="7" t="n"/>
-      <c r="O26" s="7" t="n"/>
-      <c r="P26" s="7" t="n"/>
-      <c r="Q26" s="7" t="n"/>
-      <c r="R26" s="6" t="n"/>
-      <c r="S26" s="7" t="n"/>
-      <c r="T26" s="7" t="n"/>
-      <c r="U26" s="7" t="n"/>
-      <c r="V26" s="7" t="n"/>
-      <c r="W26" s="7" t="n"/>
+      <c r="L26" s="54" t="n"/>
+      <c r="M26" s="54" t="n"/>
+      <c r="N26" s="54" t="n"/>
+      <c r="O26" s="54" t="n"/>
+      <c r="P26" s="54" t="n"/>
+      <c r="Q26" s="54" t="n"/>
+      <c r="R26" s="57" t="n"/>
+      <c r="S26" s="54" t="n"/>
+      <c r="T26" s="54" t="n"/>
+      <c r="U26" s="54" t="n"/>
+      <c r="V26" s="54" t="n"/>
+      <c r="W26" s="54" t="n"/>
     </row>
     <row r="27" ht="20.1" customHeight="1">
-      <c r="A27" s="11" t="n"/>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="10" t="n"/>
-      <c r="F27" s="10" t="n"/>
-      <c r="G27" s="9" t="n"/>
-      <c r="H27" s="11" t="n"/>
-      <c r="I27" s="10" t="n"/>
-      <c r="J27" s="10" t="n"/>
-      <c r="K27" s="10" t="n"/>
-      <c r="L27" s="10" t="n"/>
-      <c r="M27" s="10" t="n"/>
-      <c r="N27" s="10" t="n"/>
-      <c r="O27" s="10" t="n"/>
-      <c r="P27" s="10" t="n"/>
-      <c r="Q27" s="10" t="n"/>
-      <c r="R27" s="9" t="n"/>
-      <c r="S27" s="7" t="n"/>
-      <c r="T27" s="7" t="n"/>
-      <c r="U27" s="7" t="n"/>
-      <c r="V27" s="7" t="n"/>
-      <c r="W27" s="7" t="n"/>
+      <c r="A27" s="51" t="n"/>
+      <c r="B27" s="52" t="n"/>
+      <c r="C27" s="52" t="n"/>
+      <c r="D27" s="52" t="n"/>
+      <c r="E27" s="52" t="n"/>
+      <c r="F27" s="52" t="n"/>
+      <c r="G27" s="53" t="n"/>
+      <c r="H27" s="51" t="n"/>
+      <c r="I27" s="52" t="n"/>
+      <c r="J27" s="52" t="n"/>
+      <c r="K27" s="52" t="n"/>
+      <c r="L27" s="52" t="n"/>
+      <c r="M27" s="52" t="n"/>
+      <c r="N27" s="52" t="n"/>
+      <c r="O27" s="52" t="n"/>
+      <c r="P27" s="52" t="n"/>
+      <c r="Q27" s="52" t="n"/>
+      <c r="R27" s="53" t="n"/>
+      <c r="S27" s="54" t="n"/>
+      <c r="T27" s="54" t="n"/>
+      <c r="U27" s="54" t="n"/>
+      <c r="V27" s="54" t="n"/>
+      <c r="W27" s="54" t="n"/>
     </row>
     <row r="28" ht="20.1" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="60" t="inlineStr">
         <is>
           <t>حقل مخصص للصندوق:</t>
         </is>
       </c>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="14" t="n"/>
-      <c r="G28" s="13" t="n"/>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="B28" s="54" t="n"/>
+      <c r="C28" s="54" t="n"/>
+      <c r="D28" s="54" t="n"/>
+      <c r="E28" s="54" t="n"/>
+      <c r="F28" s="82" t="n"/>
+      <c r="G28" s="59" t="n"/>
+      <c r="H28" s="54" t="inlineStr">
         <is>
           <t>عولج في دائرة التسجيل...................................</t>
         </is>
       </c>
-      <c r="I28" s="7" t="n"/>
-      <c r="J28" s="7" t="n"/>
-      <c r="K28" s="7" t="n"/>
-      <c r="L28" s="7" t="n"/>
-      <c r="M28" s="7" t="n"/>
-      <c r="N28" s="7" t="n"/>
-      <c r="O28" s="7" t="n"/>
-      <c r="P28" s="7" t="n"/>
-      <c r="Q28" s="7" t="n"/>
-      <c r="R28" s="6" t="n"/>
-      <c r="S28" s="7" t="n"/>
-      <c r="T28" s="7" t="n"/>
-      <c r="U28" s="7" t="n"/>
-      <c r="V28" s="7" t="n"/>
-      <c r="W28" s="7" t="n"/>
+      <c r="I28" s="54" t="n"/>
+      <c r="J28" s="54" t="n"/>
+      <c r="K28" s="54" t="n"/>
+      <c r="L28" s="54" t="n"/>
+      <c r="M28" s="54" t="n"/>
+      <c r="N28" s="54" t="n"/>
+      <c r="O28" s="54" t="n"/>
+      <c r="P28" s="54" t="n"/>
+      <c r="Q28" s="54" t="n"/>
+      <c r="R28" s="57" t="n"/>
+      <c r="S28" s="54" t="n"/>
+      <c r="T28" s="54" t="n"/>
+      <c r="U28" s="54" t="n"/>
+      <c r="V28" s="54" t="n"/>
+      <c r="W28" s="54" t="n"/>
     </row>
     <row r="29" ht="20.1" customHeight="1">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="60" t="inlineStr">
         <is>
           <t>عولج في مركز رقم:.......................................</t>
         </is>
       </c>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="14" t="n"/>
-      <c r="G29" s="13" t="n"/>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="B29" s="54" t="n"/>
+      <c r="C29" s="54" t="n"/>
+      <c r="D29" s="54" t="n"/>
+      <c r="E29" s="54" t="n"/>
+      <c r="F29" s="82" t="n"/>
+      <c r="G29" s="59" t="n"/>
+      <c r="H29" s="54" t="inlineStr">
         <is>
           <t>بتاريخ:.....................................................</t>
         </is>
       </c>
-      <c r="I29" s="7" t="n"/>
-      <c r="J29" s="7" t="n"/>
-      <c r="K29" s="7" t="n"/>
-      <c r="L29" s="7" t="n"/>
-      <c r="M29" s="7" t="n"/>
-      <c r="N29" s="7" t="n"/>
-      <c r="O29" s="7" t="n"/>
-      <c r="P29" s="7" t="n"/>
-      <c r="Q29" s="7" t="n"/>
-      <c r="R29" s="6" t="n"/>
-      <c r="S29" s="7" t="n"/>
-      <c r="T29" s="7" t="n"/>
-      <c r="U29" s="7" t="n"/>
-      <c r="V29" s="7" t="n"/>
-      <c r="W29" s="7" t="n"/>
+      <c r="I29" s="54" t="n"/>
+      <c r="J29" s="54" t="n"/>
+      <c r="K29" s="54" t="n"/>
+      <c r="L29" s="54" t="n"/>
+      <c r="M29" s="54" t="n"/>
+      <c r="N29" s="54" t="n"/>
+      <c r="O29" s="54" t="n"/>
+      <c r="P29" s="54" t="n"/>
+      <c r="Q29" s="54" t="n"/>
+      <c r="R29" s="57" t="n"/>
+      <c r="S29" s="54" t="n"/>
+      <c r="T29" s="54" t="n"/>
+      <c r="U29" s="54" t="n"/>
+      <c r="V29" s="54" t="n"/>
+      <c r="W29" s="54" t="n"/>
     </row>
     <row r="30" ht="20.1" customHeight="1">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="60" t="inlineStr">
         <is>
           <t>بتاريخ:......................................................</t>
         </is>
       </c>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="7" t="n"/>
-      <c r="I30" s="7" t="n"/>
-      <c r="J30" s="7" t="n"/>
-      <c r="K30" s="7" t="n"/>
-      <c r="L30" s="7" t="n"/>
-      <c r="M30" s="7" t="n"/>
-      <c r="N30" s="7" t="n"/>
-      <c r="O30" s="7" t="n"/>
-      <c r="P30" s="7" t="n"/>
-      <c r="Q30" s="7" t="n"/>
-      <c r="R30" s="6" t="n"/>
-      <c r="S30" s="7" t="n"/>
-      <c r="T30" s="7" t="n"/>
-      <c r="U30" s="7" t="n"/>
-      <c r="V30" s="7" t="n"/>
-      <c r="W30" s="7" t="n"/>
+      <c r="B30" s="54" t="n"/>
+      <c r="C30" s="54" t="n"/>
+      <c r="D30" s="54" t="n"/>
+      <c r="E30" s="54" t="n"/>
+      <c r="F30" s="54" t="n"/>
+      <c r="G30" s="57" t="n"/>
+      <c r="H30" s="54" t="n"/>
+      <c r="I30" s="54" t="n"/>
+      <c r="J30" s="54" t="n"/>
+      <c r="K30" s="54" t="n"/>
+      <c r="L30" s="54" t="n"/>
+      <c r="M30" s="54" t="n"/>
+      <c r="N30" s="54" t="n"/>
+      <c r="O30" s="54" t="n"/>
+      <c r="P30" s="54" t="n"/>
+      <c r="Q30" s="54" t="n"/>
+      <c r="R30" s="57" t="n"/>
+      <c r="S30" s="54" t="n"/>
+      <c r="T30" s="54" t="n"/>
+      <c r="U30" s="54" t="n"/>
+      <c r="V30" s="54" t="n"/>
+      <c r="W30" s="54" t="n"/>
     </row>
     <row r="31" ht="20.1" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="60" t="inlineStr">
         <is>
           <t>اسم وتوقيع المستخدم.......................................</t>
         </is>
       </c>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="14" t="n"/>
-      <c r="G31" s="13" t="n"/>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="B31" s="54" t="n"/>
+      <c r="C31" s="54" t="n"/>
+      <c r="D31" s="54" t="n"/>
+      <c r="E31" s="54" t="n"/>
+      <c r="F31" s="82" t="n"/>
+      <c r="G31" s="59" t="n"/>
+      <c r="H31" s="54" t="inlineStr">
         <is>
           <t>اسم وتوقيع المستخدم......................................</t>
         </is>
       </c>
-      <c r="I31" s="7" t="n"/>
-      <c r="J31" s="7" t="n"/>
-      <c r="K31" s="7" t="n"/>
-      <c r="L31" s="7" t="n"/>
-      <c r="M31" s="7" t="n"/>
-      <c r="N31" s="7" t="n"/>
-      <c r="O31" s="7" t="n"/>
-      <c r="P31" s="7" t="n"/>
-      <c r="Q31" s="7" t="n"/>
-      <c r="R31" s="6" t="n"/>
-      <c r="S31" s="7" t="n"/>
-      <c r="T31" s="7" t="n"/>
-      <c r="U31" s="7" t="n"/>
-      <c r="V31" s="7" t="n"/>
-      <c r="W31" s="7" t="n"/>
+      <c r="I31" s="54" t="n"/>
+      <c r="J31" s="54" t="n"/>
+      <c r="K31" s="54" t="n"/>
+      <c r="L31" s="54" t="n"/>
+      <c r="M31" s="54" t="n"/>
+      <c r="N31" s="54" t="n"/>
+      <c r="O31" s="54" t="n"/>
+      <c r="P31" s="54" t="n"/>
+      <c r="Q31" s="54" t="n"/>
+      <c r="R31" s="57" t="n"/>
+      <c r="S31" s="54" t="n"/>
+      <c r="T31" s="54" t="n"/>
+      <c r="U31" s="54" t="n"/>
+      <c r="V31" s="54" t="n"/>
+      <c r="W31" s="54" t="n"/>
     </row>
     <row r="32" ht="20.1" customHeight="1">
-      <c r="A32" s="12" t="n"/>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="3" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
-      <c r="J32" s="4" t="n"/>
-      <c r="K32" s="4" t="n"/>
-      <c r="L32" s="4" t="n"/>
-      <c r="M32" s="4" t="n"/>
-      <c r="N32" s="4" t="n"/>
-      <c r="O32" s="4" t="n"/>
-      <c r="P32" s="4" t="n"/>
-      <c r="Q32" s="4" t="n"/>
-      <c r="R32" s="3" t="n"/>
-      <c r="S32" s="7" t="n"/>
-      <c r="T32" s="7" t="n"/>
-      <c r="U32" s="7" t="n"/>
-      <c r="V32" s="7" t="n"/>
-      <c r="W32" s="7" t="n"/>
+      <c r="A32" s="74" t="n"/>
+      <c r="B32" s="75" t="n"/>
+      <c r="C32" s="75" t="n"/>
+      <c r="D32" s="75" t="n"/>
+      <c r="E32" s="75" t="n"/>
+      <c r="F32" s="75" t="n"/>
+      <c r="G32" s="78" t="n"/>
+      <c r="H32" s="75" t="n"/>
+      <c r="I32" s="75" t="n"/>
+      <c r="J32" s="75" t="n"/>
+      <c r="K32" s="75" t="n"/>
+      <c r="L32" s="75" t="n"/>
+      <c r="M32" s="75" t="n"/>
+      <c r="N32" s="75" t="n"/>
+      <c r="O32" s="75" t="n"/>
+      <c r="P32" s="75" t="n"/>
+      <c r="Q32" s="75" t="n"/>
+      <c r="R32" s="78" t="n"/>
+      <c r="S32" s="54" t="n"/>
+      <c r="T32" s="54" t="n"/>
+      <c r="U32" s="54" t="n"/>
+      <c r="V32" s="54" t="n"/>
+      <c r="W32" s="54" t="n"/>
     </row>
     <row r="33" ht="5.1" customHeight="1">
-      <c r="A33" s="11" t="n"/>
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10" t="n"/>
-      <c r="E33" s="10" t="n"/>
-      <c r="F33" s="10" t="n"/>
-      <c r="G33" s="10" t="n"/>
-      <c r="H33" s="10" t="n"/>
-      <c r="I33" s="10" t="n"/>
-      <c r="J33" s="10" t="n"/>
-      <c r="K33" s="10" t="n"/>
-      <c r="L33" s="10" t="n"/>
-      <c r="M33" s="10" t="n"/>
-      <c r="N33" s="10" t="n"/>
-      <c r="O33" s="10" t="n"/>
-      <c r="P33" s="10" t="n"/>
-      <c r="Q33" s="10" t="n"/>
-      <c r="R33" s="9" t="n"/>
-      <c r="S33" s="7" t="n"/>
-      <c r="T33" s="7" t="n"/>
-      <c r="U33" s="7" t="n"/>
-      <c r="V33" s="7" t="n"/>
-      <c r="W33" s="7" t="n"/>
+      <c r="A33" s="51" t="n"/>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+      <c r="E33" s="52" t="n"/>
+      <c r="F33" s="52" t="n"/>
+      <c r="G33" s="52" t="n"/>
+      <c r="H33" s="52" t="n"/>
+      <c r="I33" s="52" t="n"/>
+      <c r="J33" s="52" t="n"/>
+      <c r="K33" s="52" t="n"/>
+      <c r="L33" s="52" t="n"/>
+      <c r="M33" s="52" t="n"/>
+      <c r="N33" s="52" t="n"/>
+      <c r="O33" s="52" t="n"/>
+      <c r="P33" s="52" t="n"/>
+      <c r="Q33" s="52" t="n"/>
+      <c r="R33" s="53" t="n"/>
+      <c r="S33" s="54" t="n"/>
+      <c r="T33" s="54" t="n"/>
+      <c r="U33" s="54" t="n"/>
+      <c r="V33" s="54" t="n"/>
+      <c r="W33" s="54" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="60" t="inlineStr">
         <is>
           <t>(1) تملأ المؤسسة هذه المطبوعة، وترسلها الى الصندوق الوطني للضمان الاجتماعي، كلما ترك أحد الاجراء المرتبطين بها</t>
         </is>
       </c>
-      <c r="B34" s="7" t="n"/>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="7" t="n"/>
-      <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n"/>
-      <c r="I34" s="7" t="n"/>
-      <c r="J34" s="7" t="n"/>
-      <c r="K34" s="7" t="n"/>
-      <c r="L34" s="7" t="n"/>
-      <c r="M34" s="7" t="n"/>
-      <c r="N34" s="7" t="n"/>
-      <c r="O34" s="7" t="n"/>
-      <c r="P34" s="7" t="n"/>
-      <c r="Q34" s="7" t="n"/>
-      <c r="R34" s="6" t="n"/>
-      <c r="S34" s="7" t="n"/>
-      <c r="T34" s="7" t="n"/>
-      <c r="U34" s="7" t="n"/>
-      <c r="V34" s="7" t="n"/>
-      <c r="W34" s="7" t="n"/>
+      <c r="B34" s="54" t="n"/>
+      <c r="C34" s="54" t="n"/>
+      <c r="D34" s="54" t="n"/>
+      <c r="E34" s="54" t="n"/>
+      <c r="F34" s="54" t="n"/>
+      <c r="G34" s="54" t="n"/>
+      <c r="H34" s="54" t="n"/>
+      <c r="I34" s="54" t="n"/>
+      <c r="J34" s="54" t="n"/>
+      <c r="K34" s="54" t="n"/>
+      <c r="L34" s="54" t="n"/>
+      <c r="M34" s="54" t="n"/>
+      <c r="N34" s="54" t="n"/>
+      <c r="O34" s="54" t="n"/>
+      <c r="P34" s="54" t="n"/>
+      <c r="Q34" s="54" t="n"/>
+      <c r="R34" s="57" t="n"/>
+      <c r="S34" s="54" t="n"/>
+      <c r="T34" s="54" t="n"/>
+      <c r="U34" s="54" t="n"/>
+      <c r="V34" s="54" t="n"/>
+      <c r="W34" s="54" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="60" t="inlineStr">
         <is>
           <t>عمله فيها مهما كان السبب. وذلك خلال(15) يوما من تاريخ الترك(المادة80 فقرة"4" )</t>
         </is>
       </c>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="n"/>
-      <c r="E35" s="7" t="n"/>
-      <c r="F35" s="7" t="n"/>
-      <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="n"/>
-      <c r="I35" s="7" t="n"/>
-      <c r="J35" s="7" t="n"/>
-      <c r="K35" s="7" t="n"/>
-      <c r="L35" s="7" t="n"/>
-      <c r="M35" s="7" t="n"/>
-      <c r="N35" s="7" t="n"/>
-      <c r="O35" s="7" t="n"/>
-      <c r="P35" s="7" t="n"/>
-      <c r="Q35" s="7" t="n"/>
-      <c r="R35" s="6" t="n"/>
-      <c r="S35" s="7" t="n"/>
-      <c r="T35" s="7" t="n"/>
-      <c r="U35" s="7" t="n"/>
-      <c r="V35" s="7" t="n"/>
-      <c r="W35" s="7" t="n"/>
+      <c r="B35" s="54" t="n"/>
+      <c r="C35" s="54" t="n"/>
+      <c r="D35" s="54" t="n"/>
+      <c r="E35" s="54" t="n"/>
+      <c r="F35" s="54" t="n"/>
+      <c r="G35" s="54" t="n"/>
+      <c r="H35" s="54" t="n"/>
+      <c r="I35" s="54" t="n"/>
+      <c r="J35" s="54" t="n"/>
+      <c r="K35" s="54" t="n"/>
+      <c r="L35" s="54" t="n"/>
+      <c r="M35" s="54" t="n"/>
+      <c r="N35" s="54" t="n"/>
+      <c r="O35" s="54" t="n"/>
+      <c r="P35" s="54" t="n"/>
+      <c r="Q35" s="54" t="n"/>
+      <c r="R35" s="57" t="n"/>
+      <c r="S35" s="54" t="n"/>
+      <c r="T35" s="54" t="n"/>
+      <c r="U35" s="54" t="n"/>
+      <c r="V35" s="54" t="n"/>
+      <c r="W35" s="54" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" s="74" t="inlineStr">
         <is>
           <t>* تنبيه: طائلة أهمال المطبوعة: يجب دائما ذكر رقم المؤسسة ورقم الأجير أو تاريخ ولادته بخط واضح ومقروء.</t>
         </is>
       </c>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="4" t="n"/>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="4" t="n"/>
-      <c r="I36" s="4" t="n"/>
-      <c r="J36" s="4" t="n"/>
-      <c r="K36" s="4" t="n"/>
-      <c r="L36" s="4" t="n"/>
-      <c r="M36" s="4" t="n"/>
-      <c r="N36" s="4" t="n"/>
-      <c r="O36" s="4" t="n"/>
-      <c r="P36" s="4" t="n"/>
-      <c r="Q36" s="4" t="n"/>
-      <c r="R36" s="3" t="n"/>
-      <c r="S36" s="7" t="n"/>
-      <c r="T36" s="7" t="n"/>
-      <c r="U36" s="7" t="n"/>
-      <c r="V36" s="7" t="n"/>
-      <c r="W36" s="7" t="n"/>
+      <c r="B36" s="75" t="n"/>
+      <c r="C36" s="75" t="n"/>
+      <c r="D36" s="75" t="n"/>
+      <c r="E36" s="75" t="n"/>
+      <c r="F36" s="75" t="n"/>
+      <c r="G36" s="75" t="n"/>
+      <c r="H36" s="75" t="n"/>
+      <c r="I36" s="75" t="n"/>
+      <c r="J36" s="75" t="n"/>
+      <c r="K36" s="75" t="n"/>
+      <c r="L36" s="75" t="n"/>
+      <c r="M36" s="75" t="n"/>
+      <c r="N36" s="75" t="n"/>
+      <c r="O36" s="75" t="n"/>
+      <c r="P36" s="75" t="n"/>
+      <c r="Q36" s="75" t="n"/>
+      <c r="R36" s="78" t="n"/>
+      <c r="S36" s="54" t="n"/>
+      <c r="T36" s="54" t="n"/>
+      <c r="U36" s="54" t="n"/>
+      <c r="V36" s="54" t="n"/>
+      <c r="W36" s="54" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="n"/>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="n"/>
-      <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="n"/>
-      <c r="G37" s="7" t="n"/>
-      <c r="H37" s="7" t="n"/>
-      <c r="I37" s="7" t="n"/>
-      <c r="J37" s="7" t="n"/>
-      <c r="K37" s="7" t="n"/>
-      <c r="L37" s="7" t="n"/>
-      <c r="M37" s="7" t="n"/>
-      <c r="N37" s="7" t="n"/>
-      <c r="O37" s="7" t="n"/>
-      <c r="P37" s="7" t="n"/>
-      <c r="Q37" s="7" t="n"/>
-      <c r="R37" s="7" t="n"/>
-      <c r="S37" s="7" t="n"/>
-      <c r="T37" s="7" t="n"/>
-      <c r="U37" s="7" t="n"/>
-      <c r="V37" s="7" t="n"/>
-      <c r="W37" s="7" t="n"/>
+      <c r="A37" s="54" t="n"/>
+      <c r="B37" s="54" t="n"/>
+      <c r="C37" s="54" t="n"/>
+      <c r="D37" s="54" t="n"/>
+      <c r="E37" s="54" t="n"/>
+      <c r="F37" s="54" t="n"/>
+      <c r="G37" s="54" t="n"/>
+      <c r="H37" s="54" t="n"/>
+      <c r="I37" s="54" t="n"/>
+      <c r="J37" s="54" t="n"/>
+      <c r="K37" s="54" t="n"/>
+      <c r="L37" s="54" t="n"/>
+      <c r="M37" s="54" t="n"/>
+      <c r="N37" s="54" t="n"/>
+      <c r="O37" s="54" t="n"/>
+      <c r="P37" s="54" t="n"/>
+      <c r="Q37" s="54" t="n"/>
+      <c r="R37" s="54" t="n"/>
+      <c r="S37" s="54" t="n"/>
+      <c r="T37" s="54" t="n"/>
+      <c r="U37" s="54" t="n"/>
+      <c r="V37" s="54" t="n"/>
+      <c r="W37" s="54" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="7" t="n"/>
-      <c r="B38" s="7" t="n"/>
-      <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
-      <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="n"/>
-      <c r="G38" s="7" t="n"/>
-      <c r="H38" s="7" t="n"/>
-      <c r="I38" s="7" t="n"/>
-      <c r="J38" s="7" t="n"/>
-      <c r="K38" s="7" t="n"/>
-      <c r="L38" s="7" t="n"/>
-      <c r="M38" s="7" t="n"/>
-      <c r="N38" s="7" t="n"/>
-      <c r="O38" s="7" t="n"/>
-      <c r="P38" s="7" t="n"/>
-      <c r="Q38" s="7" t="n"/>
-      <c r="R38" s="7" t="n"/>
-      <c r="S38" s="7" t="n"/>
-      <c r="T38" s="7" t="n"/>
-      <c r="U38" s="7" t="n"/>
-      <c r="V38" s="7" t="n"/>
-      <c r="W38" s="7" t="n"/>
+      <c r="A38" s="54" t="n"/>
+      <c r="B38" s="54" t="n"/>
+      <c r="C38" s="54" t="n"/>
+      <c r="D38" s="54" t="n"/>
+      <c r="E38" s="54" t="n"/>
+      <c r="F38" s="54" t="n"/>
+      <c r="G38" s="54" t="n"/>
+      <c r="H38" s="54" t="n"/>
+      <c r="I38" s="54" t="n"/>
+      <c r="J38" s="54" t="n"/>
+      <c r="K38" s="54" t="n"/>
+      <c r="L38" s="54" t="n"/>
+      <c r="M38" s="54" t="n"/>
+      <c r="N38" s="54" t="n"/>
+      <c r="O38" s="54" t="n"/>
+      <c r="P38" s="54" t="n"/>
+      <c r="Q38" s="54" t="n"/>
+      <c r="R38" s="54" t="n"/>
+      <c r="S38" s="54" t="n"/>
+      <c r="T38" s="54" t="n"/>
+      <c r="U38" s="54" t="n"/>
+      <c r="V38" s="54" t="n"/>
+      <c r="W38" s="54" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/assets/templates/cnss_leave.xlsx
+++ b/assets/templates/cnss_leave.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="اعلام ترك اجير" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'اعلام ترك اجير'!$A$1:$W$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'اعلام ترك اجير'!$A$1:$R$38</definedName>
   </definedNames>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
 </workbook>
@@ -238,7 +238,7 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -832,7 +832,7 @@
     <col width="9.21875" customWidth="1" style="14" min="19" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.1" customHeight="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="51" t="inlineStr">
         <is>
           <t>الصندوق الوطني</t>
@@ -861,7 +861,7 @@
       <c r="V1" s="54" t="n"/>
       <c r="W1" s="54" t="n"/>
     </row>
-    <row r="2" ht="20.1" customHeight="1">
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="55" t="inlineStr">
         <is>
           <t>للضمان الاجتماعي</t>
@@ -889,33 +889,33 @@
       <c r="V2" s="54" t="n"/>
       <c r="W2" s="54" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3" ht="19.7" customHeight="1">
       <c r="A3" s="58" t="inlineStr">
         <is>
           <t>اعــــــــــــــــــــــلام</t>
         </is>
       </c>
-      <c r="R3" s="59" t="n"/>
+      <c r="R3" s="49" t="n"/>
       <c r="S3" s="54" t="n"/>
       <c r="T3" s="54" t="n"/>
       <c r="U3" s="54" t="n"/>
       <c r="V3" s="54" t="n"/>
       <c r="W3" s="54" t="n"/>
     </row>
-    <row r="4" ht="18" customHeight="1">
+    <row r="4" ht="19.7" customHeight="1">
       <c r="A4" s="58" t="inlineStr">
         <is>
           <t>عن ترك أجير عمله في المؤسسة (1)</t>
         </is>
       </c>
-      <c r="R4" s="59" t="n"/>
+      <c r="R4" s="49" t="n"/>
       <c r="S4" s="54" t="n"/>
       <c r="T4" s="54" t="n"/>
       <c r="U4" s="54" t="n"/>
       <c r="V4" s="54" t="n"/>
       <c r="W4" s="54" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="19.1" customHeight="1">
       <c r="A5" s="60" t="n"/>
       <c r="B5" s="54" t="n"/>
       <c r="C5" s="54" t="n"/>
@@ -940,7 +940,7 @@
       <c r="V5" s="54" t="n"/>
       <c r="W5" s="54" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="19.1" customHeight="1">
       <c r="A6" s="60" t="n"/>
       <c r="B6" s="54" t="n"/>
       <c r="C6" s="54" t="n"/>
@@ -965,7 +965,7 @@
       <c r="V6" s="54" t="n"/>
       <c r="W6" s="54" t="n"/>
     </row>
-    <row r="7" ht="22.05" customHeight="1">
+    <row r="7" ht="24.1" customHeight="1">
       <c r="A7" s="60" t="inlineStr">
         <is>
           <t>ان صاحب العمل الموقع ادناه،</t>
@@ -994,7 +994,7 @@
       <c r="V7" s="54" t="n"/>
       <c r="W7" s="54" t="n"/>
     </row>
-    <row r="8" ht="22.05" customHeight="1">
+    <row r="8" ht="24.1" customHeight="1">
       <c r="A8" s="60" t="inlineStr">
         <is>
           <t>المسؤول عن مؤسسة :</t>
@@ -1023,7 +1023,7 @@
       <c r="V8" s="54" t="n"/>
       <c r="W8" s="54" t="n"/>
     </row>
-    <row r="9" ht="22.05" customHeight="1">
+    <row r="9" ht="24.1" customHeight="1">
       <c r="A9" s="60" t="inlineStr">
         <is>
           <t>المسجلة في الصندوق الوطني للضمان الاجتماعي تحت رقم:</t>
@@ -1052,7 +1052,7 @@
       <c r="V9" s="54" t="n"/>
       <c r="W9" s="54" t="n"/>
     </row>
-    <row r="10" ht="22.05" customHeight="1">
+    <row r="10" ht="24.1" customHeight="1">
       <c r="A10" s="60" t="inlineStr">
         <is>
           <t>سجل تجاري: مكان................................... رقم.............................. هاتف</t>
@@ -1080,7 +1080,7 @@
       <c r="V10" s="54" t="n"/>
       <c r="W10" s="54" t="n"/>
     </row>
-    <row r="11" ht="22.05" customHeight="1">
+    <row r="11" ht="24.1" customHeight="1">
       <c r="A11" s="60" t="inlineStr">
         <is>
           <t>وعنوانها الكامل:</t>
@@ -1109,7 +1109,7 @@
       <c r="V11" s="54" t="n"/>
       <c r="W11" s="54" t="n"/>
     </row>
-    <row r="12" ht="22.05" customHeight="1">
+    <row r="12" ht="24.1" customHeight="1">
       <c r="A12" s="60" t="inlineStr">
         <is>
           <t>...............................................................................................................................</t>
@@ -1138,7 +1138,7 @@
       <c r="V12" s="54" t="n"/>
       <c r="W12" s="54" t="n"/>
     </row>
-    <row r="13" ht="22.05" customHeight="1">
+    <row r="13" ht="24.1" customHeight="1">
       <c r="A13" s="60" t="inlineStr">
         <is>
           <t>يصرح بأن الأجير المبينة هويته فيما يلي والمسجل في الصندوق تحت الرقم</t>
@@ -1157,7 +1157,7 @@
       <c r="L13" s="54" t="n"/>
       <c r="M13" s="54" t="n"/>
       <c r="N13" s="63" t="n"/>
-      <c r="O13" s="65" t="n"/>
+      <c r="O13" s="50" t="n"/>
       <c r="P13" s="66" t="n"/>
       <c r="Q13" s="54" t="n"/>
       <c r="R13" s="57" t="n"/>
@@ -1167,7 +1167,7 @@
       <c r="V13" s="54" t="n"/>
       <c r="W13" s="54" t="n"/>
     </row>
-    <row r="14" ht="22.05" customHeight="1">
+    <row r="14" ht="24.1" customHeight="1">
       <c r="A14" s="60" t="inlineStr">
         <is>
           <t>الجنس:</t>
@@ -1212,7 +1212,7 @@
       <c r="V14" s="54" t="n"/>
       <c r="W14" s="54" t="n"/>
     </row>
-    <row r="15" ht="22.05" customHeight="1">
+    <row r="15" ht="24.1" customHeight="1">
       <c r="A15" s="60" t="inlineStr">
         <is>
           <t>اسم الأجير:</t>
@@ -1245,7 +1245,7 @@
       <c r="V15" s="54" t="n"/>
       <c r="W15" s="54" t="n"/>
     </row>
-    <row r="16" ht="22.05" customHeight="1">
+    <row r="16" ht="24.1" customHeight="1">
       <c r="A16" s="60" t="inlineStr">
         <is>
           <t>اسم الاب:</t>
@@ -1278,7 +1278,7 @@
       <c r="V16" s="54" t="n"/>
       <c r="W16" s="54" t="n"/>
     </row>
-    <row r="17" ht="22.05" customHeight="1">
+    <row r="17" ht="24.1" customHeight="1">
       <c r="A17" s="60" t="inlineStr">
         <is>
           <t>تاريخ ومحل ولادة الاجير:</t>
@@ -1314,7 +1314,7 @@
       <c r="V17" s="54" t="n"/>
       <c r="W17" s="54" t="n"/>
     </row>
-    <row r="18" ht="22.05" customHeight="1">
+    <row r="18" ht="24.1" customHeight="1">
       <c r="A18" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">الوضع العائلي: أعزب </t>
@@ -1379,7 +1379,7 @@
       <c r="V18" s="54" t="n"/>
       <c r="W18" s="54" t="n"/>
     </row>
-    <row r="19" ht="22.05" customHeight="1">
+    <row r="19" ht="24.1" customHeight="1">
       <c r="A19" s="60" t="inlineStr">
         <is>
           <t>ترك العمل بها منذ:</t>
@@ -1412,7 +1412,7 @@
       <c r="V19" s="54" t="n"/>
       <c r="W19" s="54" t="n"/>
     </row>
-    <row r="20" ht="22.05" customHeight="1">
+    <row r="20" ht="24.1" customHeight="1">
       <c r="A20" s="60" t="inlineStr">
         <is>
           <t>سبب ترك العمل:</t>
@@ -1496,7 +1496,7 @@
       <c r="V20" s="54" t="n"/>
       <c r="W20" s="54" t="n"/>
     </row>
-    <row r="21" ht="22.05" customHeight="1">
+    <row r="21" ht="24.1" customHeight="1">
       <c r="A21" s="60" t="inlineStr">
         <is>
           <t>عمل الاجير الحالي:</t>
@@ -1525,7 +1525,7 @@
       <c r="V21" s="54" t="n"/>
       <c r="W21" s="54" t="n"/>
     </row>
-    <row r="22" ht="22.05" customHeight="1">
+    <row r="22" ht="24.1" customHeight="1">
       <c r="A22" s="60" t="inlineStr">
         <is>
           <t xml:space="preserve">ان راتب الاجير بتاريخ ترك العمل هو: </t>
@@ -1557,7 +1557,7 @@
       <c r="V22" s="54" t="n"/>
       <c r="W22" s="54" t="n"/>
     </row>
-    <row r="23" ht="25.05" customHeight="1">
+    <row r="23" ht="27.4" customHeight="1">
       <c r="A23" s="60" t="inlineStr">
         <is>
           <t>بيروت في ..........................200                       خاتم المؤسسة       اسم المسؤول عن المؤسسة وتوقيعه</t>
@@ -1586,7 +1586,7 @@
       <c r="V23" s="54" t="n"/>
       <c r="W23" s="54" t="n"/>
     </row>
-    <row r="24" ht="67.2" customHeight="1">
+    <row r="24" ht="73.5" customHeight="1">
       <c r="A24" s="74" t="n"/>
       <c r="B24" s="75" t="n"/>
       <c r="C24" s="75" t="n"/>
@@ -1611,7 +1611,7 @@
       <c r="V24" s="54" t="n"/>
       <c r="W24" s="54" t="n"/>
     </row>
-    <row r="25" ht="20.1" customHeight="1">
+    <row r="25" ht="22" customHeight="1">
       <c r="A25" s="51" t="inlineStr">
         <is>
           <t xml:space="preserve">أوافق على صحة المعلومات المدرجة أعلاه:                   </t>
@@ -1644,7 +1644,7 @@
       <c r="V25" s="54" t="n"/>
       <c r="W25" s="54" t="n"/>
     </row>
-    <row r="26" ht="20.1" customHeight="1">
+    <row r="26" ht="22" customHeight="1">
       <c r="A26" s="74" t="inlineStr">
         <is>
           <t>التاريخ...........................................</t>
@@ -1681,7 +1681,7 @@
       <c r="V26" s="54" t="n"/>
       <c r="W26" s="54" t="n"/>
     </row>
-    <row r="27" ht="20.1" customHeight="1">
+    <row r="27" ht="22" customHeight="1">
       <c r="A27" s="51" t="n"/>
       <c r="B27" s="52" t="n"/>
       <c r="C27" s="52" t="n"/>
@@ -1706,7 +1706,7 @@
       <c r="V27" s="54" t="n"/>
       <c r="W27" s="54" t="n"/>
     </row>
-    <row r="28" ht="20.1" customHeight="1">
+    <row r="28" ht="22" customHeight="1">
       <c r="A28" s="60" t="inlineStr">
         <is>
           <t>حقل مخصص للصندوق:</t>
@@ -1739,7 +1739,7 @@
       <c r="V28" s="54" t="n"/>
       <c r="W28" s="54" t="n"/>
     </row>
-    <row r="29" ht="20.1" customHeight="1">
+    <row r="29" ht="22" customHeight="1">
       <c r="A29" s="60" t="inlineStr">
         <is>
           <t>عولج في مركز رقم:.......................................</t>
@@ -1772,7 +1772,7 @@
       <c r="V29" s="54" t="n"/>
       <c r="W29" s="54" t="n"/>
     </row>
-    <row r="30" ht="20.1" customHeight="1">
+    <row r="30" ht="22" customHeight="1">
       <c r="A30" s="60" t="inlineStr">
         <is>
           <t>بتاريخ:......................................................</t>
@@ -1801,7 +1801,7 @@
       <c r="V30" s="54" t="n"/>
       <c r="W30" s="54" t="n"/>
     </row>
-    <row r="31" ht="20.1" customHeight="1">
+    <row r="31" ht="22" customHeight="1">
       <c r="A31" s="60" t="inlineStr">
         <is>
           <t>اسم وتوقيع المستخدم.......................................</t>
@@ -1834,7 +1834,7 @@
       <c r="V31" s="54" t="n"/>
       <c r="W31" s="54" t="n"/>
     </row>
-    <row r="32" ht="20.1" customHeight="1">
+    <row r="32" ht="22" customHeight="1">
       <c r="A32" s="74" t="n"/>
       <c r="B32" s="75" t="n"/>
       <c r="C32" s="75" t="n"/>
@@ -1859,7 +1859,7 @@
       <c r="V32" s="54" t="n"/>
       <c r="W32" s="54" t="n"/>
     </row>
-    <row r="33" ht="5.1" customHeight="1">
+    <row r="33" ht="5.6" customHeight="1">
       <c r="A33" s="51" t="n"/>
       <c r="B33" s="52" t="n"/>
       <c r="C33" s="52" t="n"/>
@@ -1884,7 +1884,7 @@
       <c r="V33" s="54" t="n"/>
       <c r="W33" s="54" t="n"/>
     </row>
-    <row r="34">
+    <row r="34" ht="19.1" customHeight="1">
       <c r="A34" s="60" t="inlineStr">
         <is>
           <t>(1) تملأ المؤسسة هذه المطبوعة، وترسلها الى الصندوق الوطني للضمان الاجتماعي، كلما ترك أحد الاجراء المرتبطين بها</t>
@@ -1913,7 +1913,7 @@
       <c r="V34" s="54" t="n"/>
       <c r="W34" s="54" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" ht="19.1" customHeight="1">
       <c r="A35" s="60" t="inlineStr">
         <is>
           <t>عمله فيها مهما كان السبب. وذلك خلال(15) يوما من تاريخ الترك(المادة80 فقرة"4" )</t>
@@ -1942,7 +1942,7 @@
       <c r="V35" s="54" t="n"/>
       <c r="W35" s="54" t="n"/>
     </row>
-    <row r="36">
+    <row r="36" ht="19.1" customHeight="1">
       <c r="A36" s="74" t="inlineStr">
         <is>
           <t>* تنبيه: طائلة أهمال المطبوعة: يجب دائما ذكر رقم المؤسسة ورقم الأجير أو تاريخ ولادته بخط واضح ومقروء.</t>
@@ -1971,7 +1971,7 @@
       <c r="V36" s="54" t="n"/>
       <c r="W36" s="54" t="n"/>
     </row>
-    <row r="37">
+    <row r="37" ht="19.1" customHeight="1">
       <c r="A37" s="54" t="n"/>
       <c r="B37" s="54" t="n"/>
       <c r="C37" s="54" t="n"/>
@@ -1996,7 +1996,7 @@
       <c r="V37" s="54" t="n"/>
       <c r="W37" s="54" t="n"/>
     </row>
-    <row r="38">
+    <row r="38" ht="19.1" customHeight="1">
       <c r="A38" s="54" t="n"/>
       <c r="B38" s="54" t="n"/>
       <c r="C38" s="54" t="n"/>
@@ -2031,7 +2031,7 @@
     <mergeCell ref="F17:G17"/>
     <mergeCell ref="A4:R4"/>
   </mergeCells>
-  <printOptions horizontalCentered="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.5" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
